--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -59067,27 +59067,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -59097,26 +59097,26 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L215" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -59134,22 +59134,22 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>8.4</v>
+        <v>13.7</v>
       </c>
       <c r="Q215" t="n">
-        <v>41.2</v>
+        <v>33.7</v>
       </c>
       <c r="R215" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S215" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T215" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U215" t="n">
-        <v>24.9</v>
+        <v>50</v>
       </c>
       <c r="V215" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
@@ -59188,7 +59188,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr"/>
@@ -59200,17 +59200,17 @@
       </c>
       <c r="AG215" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ215" t="inlineStr">
@@ -59220,12 +59220,12 @@
       </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Recent form unavailable</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
@@ -59235,80 +59235,104 @@
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>96.2648</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
         <is>
-          <t>0.3798</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>0.0977</t>
-        </is>
-      </c>
-      <c r="BA215" t="inlineStr"/>
-      <c r="BB215" t="inlineStr"/>
-      <c r="BC215" t="inlineStr"/>
-      <c r="BD215" t="inlineStr"/>
-      <c r="BE215" t="inlineStr"/>
-      <c r="BF215" t="inlineStr"/>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="BB215" t="inlineStr">
+        <is>
+          <t>34.94</t>
+        </is>
+      </c>
+      <c r="BC215" t="inlineStr">
+        <is>
+          <t>88.08</t>
+        </is>
+      </c>
+      <c r="BD215" t="inlineStr">
+        <is>
+          <t>0.3902</t>
+        </is>
+      </c>
+      <c r="BE215" t="inlineStr">
+        <is>
+          <t>0.1497</t>
+        </is>
+      </c>
+      <c r="BF215" t="inlineStr">
+        <is>
+          <t>28.36</t>
+        </is>
+      </c>
       <c r="BG215" t="inlineStr"/>
       <c r="BH215" t="inlineStr"/>
       <c r="BI215" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ215" t="inlineStr"/>
@@ -59319,27 +59343,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -59349,22 +59373,22 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L216" t="n">
@@ -59382,26 +59406,26 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P216" t="n">
-        <v>31.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q216" t="n">
-        <v>33.7</v>
+        <v>41.2</v>
       </c>
       <c r="R216" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="S216" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T216" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U216" t="n">
-        <v>19.5</v>
+        <v>24.9</v>
       </c>
       <c r="V216" t="inlineStr">
         <is>
@@ -59415,7 +59439,7 @@
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
@@ -59440,7 +59464,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr"/>
@@ -59457,12 +59481,12 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ216" t="inlineStr">
@@ -59472,12 +59496,12 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 0 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM216" t="inlineStr">
@@ -59487,104 +59511,80 @@
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>28.83</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>99.7927</t>
+          <t>96.2648</t>
         </is>
       </c>
       <c r="AR216" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.3798</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>0.2974</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>0.0927</t>
-        </is>
-      </c>
-      <c r="BA216" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB216" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
-      </c>
-      <c r="BC216" t="inlineStr">
-        <is>
-          <t>88.08</t>
-        </is>
-      </c>
-      <c r="BD216" t="inlineStr">
-        <is>
-          <t>0.3902</t>
-        </is>
-      </c>
-      <c r="BE216" t="inlineStr">
-        <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BF216" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
+          <t>0.0977</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr"/>
+      <c r="BB216" t="inlineStr"/>
+      <c r="BC216" t="inlineStr"/>
+      <c r="BD216" t="inlineStr"/>
+      <c r="BE216" t="inlineStr"/>
+      <c r="BF216" t="inlineStr"/>
       <c r="BG216" t="inlineStr"/>
       <c r="BH216" t="inlineStr"/>
       <c r="BI216" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ216" t="inlineStr"/>
@@ -59595,27 +59595,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>699393</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -59625,26 +59625,26 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L217" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
@@ -59658,26 +59658,26 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P217" t="n">
-        <v>17.5</v>
+        <v>31.4</v>
       </c>
       <c r="Q217" t="n">
-        <v>40.2</v>
+        <v>33.7</v>
       </c>
       <c r="R217" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S217" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T217" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U217" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="V217" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
@@ -59716,7 +59716,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr"/>
@@ -59733,12 +59733,12 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -59748,12 +59748,12 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 3/12, 0 HR</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
@@ -59763,80 +59763,104 @@
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>99.2705</t>
+          <t>99.7927</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>0.2974</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>0.127</t>
-        </is>
-      </c>
-      <c r="BA217" t="inlineStr"/>
-      <c r="BB217" t="inlineStr"/>
-      <c r="BC217" t="inlineStr"/>
-      <c r="BD217" t="inlineStr"/>
-      <c r="BE217" t="inlineStr"/>
-      <c r="BF217" t="inlineStr"/>
+          <t>0.0927</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="BB217" t="inlineStr">
+        <is>
+          <t>34.94</t>
+        </is>
+      </c>
+      <c r="BC217" t="inlineStr">
+        <is>
+          <t>88.08</t>
+        </is>
+      </c>
+      <c r="BD217" t="inlineStr">
+        <is>
+          <t>0.3902</t>
+        </is>
+      </c>
+      <c r="BE217" t="inlineStr">
+        <is>
+          <t>0.1497</t>
+        </is>
+      </c>
+      <c r="BF217" t="inlineStr">
+        <is>
+          <t>28.36</t>
+        </is>
+      </c>
       <c r="BG217" t="inlineStr"/>
       <c r="BH217" t="inlineStr"/>
       <c r="BI217" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ217" t="inlineStr"/>
@@ -59847,27 +59871,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>699393</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -59877,22 +59901,22 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L218" t="n">
@@ -59914,22 +59938,22 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>31.3</v>
+        <v>17.5</v>
       </c>
       <c r="Q218" t="n">
-        <v>14</v>
+        <v>40.2</v>
       </c>
       <c r="R218" t="n">
-        <v>38.7</v>
+        <v>25.4</v>
       </c>
       <c r="S218" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T218" t="n">
         <v>75</v>
       </c>
       <c r="U218" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="V218" t="inlineStr">
         <is>
@@ -59943,7 +59967,7 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
@@ -59968,7 +59992,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr"/>
@@ -59985,27 +60009,27 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
@@ -60015,104 +60039,80 @@
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>99.6133</t>
+          <t>99.2705</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.083</t>
         </is>
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.292</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>0.1149</t>
-        </is>
-      </c>
-      <c r="BA218" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="BB218" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
-      </c>
-      <c r="BC218" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="BD218" t="inlineStr">
-        <is>
-          <t>0.338</t>
-        </is>
-      </c>
-      <c r="BE218" t="inlineStr">
-        <is>
-          <t>0.106</t>
-        </is>
-      </c>
-      <c r="BF218" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+          <t>0.127</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr"/>
+      <c r="BB218" t="inlineStr"/>
+      <c r="BC218" t="inlineStr"/>
+      <c r="BD218" t="inlineStr"/>
+      <c r="BE218" t="inlineStr"/>
+      <c r="BF218" t="inlineStr"/>
       <c r="BG218" t="inlineStr"/>
       <c r="BH218" t="inlineStr"/>
       <c r="BI218" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ218" t="inlineStr"/>
@@ -60123,12 +60123,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -60153,7 +60153,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -60172,7 +60172,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
@@ -60190,22 +60190,22 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>21</v>
+        <v>31.3</v>
       </c>
       <c r="Q219" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="R219" t="n">
         <v>38.7</v>
       </c>
       <c r="S219" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T219" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U219" t="n">
-        <v>22.4</v>
+        <v>36</v>
       </c>
       <c r="V219" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
@@ -60244,7 +60244,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr"/>
@@ -60261,27 +60261,27 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
@@ -60291,67 +60291,67 @@
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>40.04</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>98.4504</t>
+          <t>99.6133</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
@@ -60399,27 +60399,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -60429,26 +60429,26 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L220" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -60466,22 +60466,22 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Q220" t="n">
-        <v>38</v>
+        <v>14.3</v>
       </c>
       <c r="R220" t="n">
-        <v>27.6</v>
+        <v>38.7</v>
       </c>
       <c r="S220" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T220" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U220" t="n">
-        <v>60.7</v>
+        <v>22.4</v>
       </c>
       <c r="V220" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -60520,7 +60520,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr"/>
@@ -60542,22 +60542,22 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
@@ -60567,104 +60567,104 @@
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>99.0171</t>
+          <t>98.4504</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>0.0946</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>0.2897</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>72.79</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>0.1157</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD220" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="BE220" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BG220" t="inlineStr"/>
       <c r="BH220" t="inlineStr"/>
       <c r="BI220" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ220" t="inlineStr"/>
@@ -60675,27 +60675,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -60705,17 +60705,17 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -60724,7 +60724,7 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -60738,26 +60738,26 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P221" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="Q221" t="n">
-        <v>45.5</v>
+        <v>38</v>
       </c>
       <c r="R221" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S221" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T221" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U221" t="n">
-        <v>18</v>
+        <v>60.7</v>
       </c>
       <c r="V221" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
@@ -60813,7 +60813,7 @@
       </c>
       <c r="AH221" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI221" t="inlineStr">
@@ -60823,17 +60823,17 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM221" t="inlineStr">
@@ -60843,104 +60843,104 @@
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>95.7821</t>
+          <t>99.0171</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>0.3316</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.0946</t>
         </is>
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.2897</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>72.79</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>0.1121</t>
+          <t>0.1157</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD221" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE221" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG221" t="inlineStr"/>
       <c r="BH221" t="inlineStr"/>
       <c r="BI221" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ221" t="inlineStr"/>
@@ -60951,27 +60951,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -60981,17 +60981,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>674003</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -61000,7 +61000,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>33.9</v>
+        <v>34.2</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -61018,22 +61018,22 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>10.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q222" t="n">
-        <v>60.9</v>
+        <v>45.5</v>
       </c>
       <c r="R222" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S222" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T222" t="n">
         <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -61072,7 +61072,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr"/>
@@ -61089,12 +61089,12 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -61104,119 +61104,119 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>96.5058</t>
+          <t>95.7821</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3316</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.2786</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.1121</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD222" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE222" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG222" t="inlineStr"/>
       <c r="BH222" t="inlineStr"/>
       <c r="BI222" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ222" t="inlineStr"/>
@@ -61227,27 +61227,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -61257,26 +61257,26 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>674003</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L223" t="n">
-        <v>33.5</v>
+        <v>33.9</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
@@ -61294,22 +61294,22 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="Q223" t="n">
-        <v>22.7</v>
+        <v>60.9</v>
       </c>
       <c r="R223" t="n">
         <v>27.6</v>
       </c>
       <c r="S223" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T223" t="n">
         <v>50</v>
       </c>
       <c r="U223" t="n">
-        <v>57.8</v>
+        <v>7</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -61348,7 +61348,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr"/>
@@ -61365,134 +61365,134 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>96.5058</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="BE223" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BG223" t="inlineStr"/>
       <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -61503,12 +61503,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -61533,7 +61533,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -61566,11 +61566,11 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>36.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q224" t="n">
         <v>22.7</v>
@@ -61579,13 +61579,13 @@
         <v>27.6</v>
       </c>
       <c r="S224" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T224" t="n">
         <v>50</v>
       </c>
       <c r="U224" t="n">
-        <v>31.9</v>
+        <v>57.8</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61624,7 +61624,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -61641,22 +61641,22 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
@@ -61671,67 +61671,67 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
@@ -61779,27 +61779,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -61809,17 +61809,17 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -61842,26 +61842,26 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>7.1</v>
+        <v>36.8</v>
       </c>
       <c r="Q225" t="n">
-        <v>39.3</v>
+        <v>22.7</v>
       </c>
       <c r="R225" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S225" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T225" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U225" t="n">
-        <v>21.5</v>
+        <v>31.9</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -61917,7 +61917,7 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
@@ -61927,17 +61927,17 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
@@ -61947,104 +61947,104 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>95.716</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1286</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD225" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE225" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG225" t="inlineStr"/>
       <c r="BH225" t="inlineStr"/>
       <c r="BI225" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ225" t="inlineStr"/>
@@ -62055,24 +62055,24 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="F226" t="inlineStr">
         <is>
           <t>2026-08-22T23:15:00Z</t>
@@ -62085,17 +62085,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62104,7 +62104,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -62122,22 +62122,22 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>23.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q226" t="n">
-        <v>35.6</v>
+        <v>39.3</v>
       </c>
       <c r="R226" t="n">
         <v>23.2</v>
       </c>
       <c r="S226" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T226" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U226" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62151,7 +62151,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62176,7 +62176,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr"/>
@@ -62193,12 +62193,12 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
@@ -62208,12 +62208,12 @@
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62223,97 +62223,97 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>99.9594</t>
+          <t>95.716</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.3073</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.1286</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
@@ -62331,27 +62331,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -62366,12 +62366,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -62398,13 +62398,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>18.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q227" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="R227" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="S227" t="n">
         <v>47.9</v>
@@ -62413,7 +62413,7 @@
         <v>75</v>
       </c>
       <c r="U227" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62469,134 +62469,134 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>97.4526</t>
+          <t>99.9594</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.3073</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
       <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ227" t="inlineStr"/>
@@ -62607,12 +62607,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -62637,7 +62637,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -62656,7 +62656,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
@@ -62670,26 +62670,26 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P228" t="n">
-        <v>26</v>
+        <v>18.6</v>
       </c>
       <c r="Q228" t="n">
-        <v>39</v>
+        <v>37.8</v>
       </c>
       <c r="R228" t="n">
         <v>22.6</v>
       </c>
       <c r="S228" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T228" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U228" t="n">
-        <v>36</v>
+        <v>24.3</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62703,7 +62703,7 @@
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -62728,7 +62728,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr"/>
@@ -62745,7 +62745,7 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
@@ -62755,17 +62755,17 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
@@ -62775,67 +62775,67 @@
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>98.8632</t>
+          <t>97.4526</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
@@ -62883,27 +62883,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>664702</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -62913,26 +62913,26 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -62946,26 +62946,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="Q229" t="n">
-        <v>45.5</v>
+        <v>39</v>
       </c>
       <c r="R229" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S229" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T229" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U229" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63004,7 +63004,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63021,134 +63021,134 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ229" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ229" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/12, 0 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>86.08</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>95.6415</t>
+          <t>98.8632</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.2894</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD229" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE229" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr"/>
       <c r="BH229" t="inlineStr"/>
       <c r="BI229" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ229" t="inlineStr"/>
@@ -63159,27 +63159,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>664702</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -63189,22 +63189,22 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -63226,22 +63226,22 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>16.3</v>
+        <v>8.4</v>
       </c>
       <c r="Q230" t="n">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="R230" t="n">
-        <v>22.6</v>
+        <v>38.2</v>
       </c>
       <c r="S230" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T230" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U230" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63255,7 +63255,7 @@
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
@@ -63297,134 +63297,134 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 0/12, 0 HR</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>86.08</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>95.6415</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.2894</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>68.12</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
       <c r="BH230" t="inlineStr"/>
       <c r="BI230" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ230" t="inlineStr"/>
@@ -63435,27 +63435,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63465,17 +63465,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63484,7 +63484,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63502,22 +63502,22 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="Q231" t="n">
-        <v>33.7</v>
+        <v>40</v>
       </c>
       <c r="R231" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S231" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T231" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63531,7 +63531,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63556,7 +63556,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr"/>
@@ -63573,134 +63573,134 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>97.0729</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -59067,27 +59067,27 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -59097,26 +59097,26 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L215" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -59134,22 +59134,22 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>13.7</v>
+        <v>8.4</v>
       </c>
       <c r="Q215" t="n">
-        <v>33.7</v>
+        <v>41.2</v>
       </c>
       <c r="R215" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="S215" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T215" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U215" t="n">
-        <v>50</v>
+        <v>24.9</v>
       </c>
       <c r="V215" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y215" t="inlineStr">
@@ -59188,7 +59188,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr"/>
@@ -59200,32 +59200,32 @@
       </c>
       <c r="AG215" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK215" t="inlineStr">
         <is>
-          <t>Recent form unavailable</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL215" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM215" t="inlineStr">
@@ -59235,104 +59235,80 @@
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.83</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AQ215" t="inlineStr">
         <is>
-          <t>97.0729</t>
+          <t>96.2648</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3798</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AT215" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>0.029</t>
-        </is>
-      </c>
-      <c r="BA215" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB215" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
-      </c>
-      <c r="BC215" t="inlineStr">
-        <is>
-          <t>88.08</t>
-        </is>
-      </c>
-      <c r="BD215" t="inlineStr">
-        <is>
-          <t>0.3902</t>
-        </is>
-      </c>
-      <c r="BE215" t="inlineStr">
-        <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BF215" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
+          <t>0.0977</t>
+        </is>
+      </c>
+      <c r="BA215" t="inlineStr"/>
+      <c r="BB215" t="inlineStr"/>
+      <c r="BC215" t="inlineStr"/>
+      <c r="BD215" t="inlineStr"/>
+      <c r="BE215" t="inlineStr"/>
+      <c r="BF215" t="inlineStr"/>
       <c r="BG215" t="inlineStr"/>
       <c r="BH215" t="inlineStr"/>
       <c r="BI215" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ215" t="inlineStr"/>
@@ -59343,27 +59319,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -59373,22 +59349,22 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L216" t="n">
@@ -59406,26 +59382,26 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P216" t="n">
-        <v>8.4</v>
+        <v>31.4</v>
       </c>
       <c r="Q216" t="n">
-        <v>41.2</v>
+        <v>33.7</v>
       </c>
       <c r="R216" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="S216" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T216" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U216" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V216" t="inlineStr">
         <is>
@@ -59439,7 +59415,7 @@
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y216" t="inlineStr">
@@ -59464,7 +59440,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr"/>
@@ -59481,12 +59457,12 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ216" t="inlineStr">
@@ -59496,12 +59472,12 @@
       </c>
       <c r="AK216" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Last 7 games: 3/12, 0 HR</t>
         </is>
       </c>
       <c r="AL216" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM216" t="inlineStr">
@@ -59511,80 +59487,104 @@
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>28.83</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ216" t="inlineStr">
         <is>
-          <t>96.2648</t>
+          <t>99.7927</t>
         </is>
       </c>
       <c r="AR216" t="inlineStr">
         <is>
-          <t>0.3798</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT216" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.2974</t>
         </is>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>0.0977</t>
-        </is>
-      </c>
-      <c r="BA216" t="inlineStr"/>
-      <c r="BB216" t="inlineStr"/>
-      <c r="BC216" t="inlineStr"/>
-      <c r="BD216" t="inlineStr"/>
-      <c r="BE216" t="inlineStr"/>
-      <c r="BF216" t="inlineStr"/>
+          <t>0.0927</t>
+        </is>
+      </c>
+      <c r="BA216" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="BB216" t="inlineStr">
+        <is>
+          <t>34.94</t>
+        </is>
+      </c>
+      <c r="BC216" t="inlineStr">
+        <is>
+          <t>88.08</t>
+        </is>
+      </c>
+      <c r="BD216" t="inlineStr">
+        <is>
+          <t>0.3902</t>
+        </is>
+      </c>
+      <c r="BE216" t="inlineStr">
+        <is>
+          <t>0.1497</t>
+        </is>
+      </c>
+      <c r="BF216" t="inlineStr">
+        <is>
+          <t>28.36</t>
+        </is>
+      </c>
       <c r="BG216" t="inlineStr"/>
       <c r="BH216" t="inlineStr"/>
       <c r="BI216" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ216" t="inlineStr"/>
@@ -59595,27 +59595,27 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>699393</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -59625,26 +59625,26 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Kade Anderson</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>807739</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L217" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
@@ -59658,26 +59658,26 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P217" t="n">
-        <v>31.4</v>
+        <v>17.5</v>
       </c>
       <c r="Q217" t="n">
-        <v>33.7</v>
+        <v>40.2</v>
       </c>
       <c r="R217" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="S217" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T217" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U217" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="V217" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr">
@@ -59716,7 +59716,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr"/>
@@ -59733,12 +59733,12 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -59748,12 +59748,12 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
@@ -59763,104 +59763,80 @@
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>99.7927</t>
+          <t>99.2705</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.083</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>0.2974</t>
+          <t>0.292</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>0.0927</t>
-        </is>
-      </c>
-      <c r="BA217" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB217" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
-      </c>
-      <c r="BC217" t="inlineStr">
-        <is>
-          <t>88.08</t>
-        </is>
-      </c>
-      <c r="BD217" t="inlineStr">
-        <is>
-          <t>0.3902</t>
-        </is>
-      </c>
-      <c r="BE217" t="inlineStr">
-        <is>
-          <t>0.1497</t>
-        </is>
-      </c>
-      <c r="BF217" t="inlineStr">
-        <is>
-          <t>28.36</t>
-        </is>
-      </c>
+          <t>0.127</t>
+        </is>
+      </c>
+      <c r="BA217" t="inlineStr"/>
+      <c r="BB217" t="inlineStr"/>
+      <c r="BC217" t="inlineStr"/>
+      <c r="BD217" t="inlineStr"/>
+      <c r="BE217" t="inlineStr"/>
+      <c r="BF217" t="inlineStr"/>
       <c r="BG217" t="inlineStr"/>
       <c r="BH217" t="inlineStr"/>
       <c r="BI217" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ217" t="inlineStr"/>
@@ -59871,27 +59847,27 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>699393</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -59901,22 +59877,22 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L218" t="n">
@@ -59938,22 +59914,22 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>17.5</v>
+        <v>31.3</v>
       </c>
       <c r="Q218" t="n">
-        <v>40.2</v>
+        <v>14</v>
       </c>
       <c r="R218" t="n">
-        <v>25.4</v>
+        <v>38.7</v>
       </c>
       <c r="S218" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T218" t="n">
         <v>75</v>
       </c>
       <c r="U218" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="V218" t="inlineStr">
         <is>
@@ -59967,7 +59943,7 @@
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y218" t="inlineStr">
@@ -59992,7 +59968,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr"/>
@@ -60009,27 +59985,27 @@
       </c>
       <c r="AH218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK218" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL218" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM218" t="inlineStr">
@@ -60039,80 +60015,104 @@
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.04</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
         <is>
-          <t>99.2705</t>
+          <t>99.6133</t>
         </is>
       </c>
       <c r="AR218" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="AT218" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>0.127</t>
-        </is>
-      </c>
-      <c r="BA218" t="inlineStr"/>
-      <c r="BB218" t="inlineStr"/>
-      <c r="BC218" t="inlineStr"/>
-      <c r="BD218" t="inlineStr"/>
-      <c r="BE218" t="inlineStr"/>
-      <c r="BF218" t="inlineStr"/>
+          <t>0.1149</t>
+        </is>
+      </c>
+      <c r="BA218" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="BB218" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="BC218" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="BD218" t="inlineStr">
+        <is>
+          <t>0.338</t>
+        </is>
+      </c>
+      <c r="BE218" t="inlineStr">
+        <is>
+          <t>0.106</t>
+        </is>
+      </c>
+      <c r="BF218" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="BG218" t="inlineStr"/>
       <c r="BH218" t="inlineStr"/>
       <c r="BI218" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ218" t="inlineStr"/>
@@ -60123,12 +60123,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -60153,7 +60153,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -60172,7 +60172,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="M219" t="inlineStr">
         <is>
@@ -60190,22 +60190,22 @@
         </is>
       </c>
       <c r="P219" t="n">
-        <v>31.3</v>
+        <v>21</v>
       </c>
       <c r="Q219" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="R219" t="n">
         <v>38.7</v>
       </c>
       <c r="S219" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T219" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U219" t="n">
-        <v>36</v>
+        <v>22.4</v>
       </c>
       <c r="V219" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
@@ -60244,7 +60244,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr"/>
@@ -60261,27 +60261,27 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL219" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
@@ -60291,67 +60291,67 @@
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
         <is>
-          <t>99.6133</t>
+          <t>98.4504</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT219" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
@@ -60399,27 +60399,27 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -60429,26 +60429,26 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L220" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="M220" t="inlineStr">
         <is>
@@ -60466,22 +60466,22 @@
         </is>
       </c>
       <c r="P220" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="Q220" t="n">
-        <v>14.3</v>
+        <v>38</v>
       </c>
       <c r="R220" t="n">
-        <v>38.7</v>
+        <v>27.6</v>
       </c>
       <c r="S220" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T220" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U220" t="n">
-        <v>22.4</v>
+        <v>60.7</v>
       </c>
       <c r="V220" t="inlineStr">
         <is>
@@ -60495,7 +60495,7 @@
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y220" t="inlineStr">
@@ -60520,7 +60520,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr"/>
@@ -60542,22 +60542,22 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL220" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM220" t="inlineStr">
@@ -60567,104 +60567,104 @@
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>98.4504</t>
+          <t>99.0171</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.0946</t>
         </is>
       </c>
       <c r="AT220" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.2897</t>
         </is>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.79</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>20.38</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1157</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>37.86</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD220" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE220" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF220" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="BG220" t="inlineStr"/>
       <c r="BH220" t="inlineStr"/>
       <c r="BI220" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ220" t="inlineStr"/>
@@ -60675,27 +60675,27 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -60705,17 +60705,17 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -60724,7 +60724,7 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="M221" t="inlineStr">
         <is>
@@ -60738,26 +60738,26 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P221" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q221" t="n">
-        <v>38</v>
+        <v>45.5</v>
       </c>
       <c r="R221" t="n">
-        <v>27.6</v>
+        <v>38.2</v>
       </c>
       <c r="S221" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T221" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U221" t="n">
-        <v>60.7</v>
+        <v>18</v>
       </c>
       <c r="V221" t="inlineStr">
         <is>
@@ -60771,7 +60771,7 @@
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
@@ -60813,7 +60813,7 @@
       </c>
       <c r="AH221" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI221" t="inlineStr">
@@ -60823,17 +60823,17 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL221" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM221" t="inlineStr">
@@ -60843,104 +60843,104 @@
       </c>
       <c r="AN221" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>99.0171</t>
+          <t>95.7821</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3316</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>0.0946</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT221" t="inlineStr">
         <is>
-          <t>0.2897</t>
+          <t>0.2786</t>
         </is>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>72.79</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>0.1157</t>
+          <t>0.1121</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD221" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE221" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF221" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG221" t="inlineStr"/>
       <c r="BH221" t="inlineStr"/>
       <c r="BI221" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ221" t="inlineStr"/>
@@ -60951,27 +60951,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -60981,17 +60981,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>674003</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -61000,7 +61000,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -61018,22 +61018,22 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>6.5</v>
+        <v>10.8</v>
       </c>
       <c r="Q222" t="n">
-        <v>45.5</v>
+        <v>60.9</v>
       </c>
       <c r="R222" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
       <c r="S222" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T222" t="n">
         <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -61072,7 +61072,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr"/>
@@ -61089,12 +61089,12 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -61104,119 +61104,119 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>95.7821</t>
+          <t>96.5058</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>0.3316</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>0.1121</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="BD222" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.511</t>
         </is>
       </c>
       <c r="BE222" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="BF222" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BG222" t="inlineStr"/>
       <c r="BH222" t="inlineStr"/>
       <c r="BI222" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ222" t="inlineStr"/>
@@ -61227,27 +61227,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -61257,26 +61257,26 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>674003</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L223" t="n">
-        <v>33.9</v>
+        <v>33.5</v>
       </c>
       <c r="M223" t="inlineStr">
         <is>
@@ -61294,22 +61294,22 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>10.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q223" t="n">
-        <v>60.9</v>
+        <v>22.7</v>
       </c>
       <c r="R223" t="n">
         <v>27.6</v>
       </c>
       <c r="S223" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T223" t="n">
         <v>50</v>
       </c>
       <c r="U223" t="n">
-        <v>7</v>
+        <v>57.8</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -61348,7 +61348,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr"/>
@@ -61365,134 +61365,134 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.2% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>96.5058</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD223" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE223" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF223" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG223" t="inlineStr"/>
       <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -61503,12 +61503,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -61533,7 +61533,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -61566,11 +61566,11 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>15.3</v>
+        <v>36.8</v>
       </c>
       <c r="Q224" t="n">
         <v>22.7</v>
@@ -61579,13 +61579,13 @@
         <v>27.6</v>
       </c>
       <c r="S224" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T224" t="n">
         <v>50</v>
       </c>
       <c r="U224" t="n">
-        <v>57.8</v>
+        <v>31.9</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61624,7 +61624,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -61641,22 +61641,22 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
@@ -61671,67 +61671,67 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
@@ -61779,27 +61779,27 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -61809,17 +61809,17 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -61842,26 +61842,26 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>36.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q225" t="n">
-        <v>22.7</v>
+        <v>39.3</v>
       </c>
       <c r="R225" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S225" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T225" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U225" t="n">
-        <v>31.9</v>
+        <v>21.5</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -61875,7 +61875,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -61917,7 +61917,7 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
@@ -61927,17 +61927,17 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
@@ -61947,104 +61947,104 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>95.716</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.1286</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD225" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE225" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF225" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG225" t="inlineStr"/>
       <c r="BH225" t="inlineStr"/>
       <c r="BI225" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ225" t="inlineStr"/>
@@ -62055,24 +62055,24 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="F226" t="inlineStr">
         <is>
           <t>2026-08-22T23:15:00Z</t>
@@ -62085,17 +62085,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62104,7 +62104,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -62122,22 +62122,22 @@
         </is>
       </c>
       <c r="P226" t="n">
-        <v>7.1</v>
+        <v>23.8</v>
       </c>
       <c r="Q226" t="n">
-        <v>39.3</v>
+        <v>35.6</v>
       </c>
       <c r="R226" t="n">
         <v>23.2</v>
       </c>
       <c r="S226" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T226" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U226" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62151,7 +62151,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62176,7 +62176,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr"/>
@@ -62193,12 +62193,12 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
@@ -62208,12 +62208,12 @@
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62223,97 +62223,97 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>95.716</t>
+          <t>99.9594</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.3073</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1286</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
@@ -62331,27 +62331,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -62366,12 +62366,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -62398,13 +62398,13 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>23.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q227" t="n">
-        <v>35.6</v>
+        <v>37.8</v>
       </c>
       <c r="R227" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="S227" t="n">
         <v>47.9</v>
@@ -62413,7 +62413,7 @@
         <v>75</v>
       </c>
       <c r="U227" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62469,134 +62469,134 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>99.9594</t>
+          <t>97.4526</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.3073</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
       <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ227" t="inlineStr"/>
@@ -62607,12 +62607,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -62637,7 +62637,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -62656,7 +62656,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="M228" t="inlineStr">
         <is>
@@ -62670,26 +62670,26 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P228" t="n">
-        <v>18.6</v>
+        <v>26</v>
       </c>
       <c r="Q228" t="n">
-        <v>37.8</v>
+        <v>39</v>
       </c>
       <c r="R228" t="n">
         <v>22.6</v>
       </c>
       <c r="S228" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T228" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U228" t="n">
-        <v>24.3</v>
+        <v>36</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62703,7 +62703,7 @@
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y228" t="inlineStr">
@@ -62728,7 +62728,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr"/>
@@ -62745,7 +62745,7 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
@@ -62755,17 +62755,17 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
@@ -62775,67 +62775,67 @@
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>97.4526</t>
+          <t>98.8632</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
@@ -62883,27 +62883,27 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>664702</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Myles Straw</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T17:35:00Z</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -62913,26 +62913,26 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Ryan Weathers</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>677960</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -62946,26 +62946,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>26</v>
+        <v>8.4</v>
       </c>
       <c r="Q229" t="n">
-        <v>39</v>
+        <v>45.5</v>
       </c>
       <c r="R229" t="n">
-        <v>22.6</v>
+        <v>38.2</v>
       </c>
       <c r="S229" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T229" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U229" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -62979,7 +62979,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63004,7 +63004,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63021,12 +63021,12 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ229" t="inlineStr">
@@ -63036,119 +63036,119 @@
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 0/12, 0 HR</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>25.21</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>86.08</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>98.8632</t>
+          <t>95.6415</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3489</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2894</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>68.12</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>36.01</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1064</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD229" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.4173</t>
         </is>
       </c>
       <c r="BE229" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF229" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BG229" t="inlineStr"/>
       <c r="BH229" t="inlineStr"/>
       <c r="BI229" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ229" t="inlineStr"/>
@@ -63159,27 +63159,27 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>664702</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Myles Straw</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2026-08-22T17:35:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -63189,22 +63189,22 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Ryan Weathers</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>677960</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -63226,22 +63226,22 @@
         </is>
       </c>
       <c r="P230" t="n">
-        <v>8.4</v>
+        <v>16.3</v>
       </c>
       <c r="Q230" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="R230" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S230" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T230" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U230" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63255,7 +63255,7 @@
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y230" t="inlineStr">
@@ -63297,134 +63297,134 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/12, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 14.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>25.21</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>86.08</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>95.6415</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3489</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.2894</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>36.01</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.1064</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.4173</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
       <c r="BH230" t="inlineStr"/>
       <c r="BI230" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ230" t="inlineStr"/>
@@ -63435,27 +63435,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63465,17 +63465,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63484,7 +63484,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>33.1</v>
+        <v>32.4</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63502,22 +63502,22 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>16.3</v>
+        <v>13.7</v>
       </c>
       <c r="Q231" t="n">
-        <v>40</v>
+        <v>33.7</v>
       </c>
       <c r="R231" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S231" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T231" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U231" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63531,7 +63531,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63556,7 +63556,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr"/>
@@ -63573,134 +63573,134 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -61607,27 +61607,27 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>681508</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Mickey Gasper</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -61637,17 +61637,17 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -61656,7 +61656,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="M224" t="inlineStr">
         <is>
@@ -61670,26 +61670,26 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P224" t="n">
-        <v>15.3</v>
+        <v>22.4</v>
       </c>
       <c r="Q224" t="n">
-        <v>22.7</v>
+        <v>25.9</v>
       </c>
       <c r="R224" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="S224" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T224" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U224" t="n">
-        <v>57.8</v>
+        <v>67</v>
       </c>
       <c r="V224" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y224" t="inlineStr">
@@ -61728,7 +61728,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr"/>
@@ -61745,27 +61745,27 @@
       </c>
       <c r="AH224" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL224" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM224" t="inlineStr">
@@ -61775,42 +61775,42 @@
       </c>
       <c r="AN224" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="AQ224" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>98.2082</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.1251</t>
         </is>
       </c>
       <c r="AT224" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
@@ -61820,59 +61820,59 @@
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.1153</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD224" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE224" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF224" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG224" t="inlineStr"/>
       <c r="BH224" t="inlineStr"/>
       <c r="BI224" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ224" t="inlineStr"/>
@@ -61883,12 +61883,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -61913,7 +61913,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -61946,11 +61946,11 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P225" t="n">
-        <v>36.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q225" t="n">
         <v>22.7</v>
@@ -61959,13 +61959,13 @@
         <v>27.6</v>
       </c>
       <c r="S225" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T225" t="n">
         <v>50</v>
       </c>
       <c r="U225" t="n">
-        <v>31.9</v>
+        <v>57.8</v>
       </c>
       <c r="V225" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -62004,7 +62004,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr"/>
@@ -62021,22 +62021,22 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL225" t="inlineStr">
@@ -62051,67 +62051,67 @@
       </c>
       <c r="AN225" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ225" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT225" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
@@ -62159,27 +62159,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -62189,17 +62189,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -62222,26 +62222,26 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>7.1</v>
+        <v>36.8</v>
       </c>
       <c r="Q226" t="n">
-        <v>39.3</v>
+        <v>22.7</v>
       </c>
       <c r="R226" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S226" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T226" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U226" t="n">
-        <v>21.5</v>
+        <v>31.9</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -62255,7 +62255,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -62297,7 +62297,7 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
@@ -62307,17 +62307,17 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -62327,104 +62327,104 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>25.11</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>85.63</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>95.716</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2945</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>40.54</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1286</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
       <c r="BH226" t="inlineStr"/>
       <c r="BI226" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ226" t="inlineStr"/>
@@ -62435,24 +62435,24 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="F227" t="inlineStr">
         <is>
           <t>2026-08-22T23:15:00Z</t>
@@ -62465,17 +62465,17 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -62484,7 +62484,7 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M227" t="inlineStr">
         <is>
@@ -62502,22 +62502,22 @@
         </is>
       </c>
       <c r="P227" t="n">
-        <v>23.8</v>
+        <v>7.1</v>
       </c>
       <c r="Q227" t="n">
-        <v>35.6</v>
+        <v>39.3</v>
       </c>
       <c r="R227" t="n">
         <v>23.2</v>
       </c>
       <c r="S227" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T227" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U227" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -62531,7 +62531,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -62556,7 +62556,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -62573,12 +62573,12 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -62588,12 +62588,12 @@
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -62603,97 +62603,97 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>39.81</t>
+          <t>25.11</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>88.73</t>
+          <t>85.63</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>99.9594</t>
+          <t>95.716</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.3073</t>
+          <t>0.2945</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>39.98</t>
+          <t>40.54</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.53</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.1291</t>
+          <t>0.1286</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
@@ -62711,27 +62711,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -62746,12 +62746,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -62778,13 +62778,13 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>18.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q228" t="n">
-        <v>37.8</v>
+        <v>35.6</v>
       </c>
       <c r="R228" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="S228" t="n">
         <v>47.9</v>
@@ -62793,7 +62793,7 @@
         <v>75</v>
       </c>
       <c r="U228" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="V228" t="inlineStr">
         <is>
@@ -62832,7 +62832,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr"/>
@@ -62849,134 +62849,134 @@
       </c>
       <c r="AH228" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 1 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL228" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM228" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN228" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>39.81</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>88.04</t>
+          <t>88.73</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>97.4526</t>
+          <t>99.9594</t>
         </is>
       </c>
       <c r="AR228" t="inlineStr">
         <is>
-          <t>0.3432</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT228" t="inlineStr">
         <is>
-          <t>0.2764</t>
+          <t>0.3073</t>
         </is>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>39.98</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.1291</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD228" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE228" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF228" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG228" t="inlineStr"/>
       <c r="BH228" t="inlineStr"/>
       <c r="BI228" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ228" t="inlineStr"/>
@@ -62987,12 +62987,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -63017,7 +63017,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -63036,7 +63036,7 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
@@ -63050,26 +63050,26 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P229" t="n">
-        <v>26</v>
+        <v>18.6</v>
       </c>
       <c r="Q229" t="n">
-        <v>39</v>
+        <v>37.8</v>
       </c>
       <c r="R229" t="n">
         <v>22.6</v>
       </c>
       <c r="S229" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T229" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U229" t="n">
-        <v>36</v>
+        <v>24.3</v>
       </c>
       <c r="V229" t="inlineStr">
         <is>
@@ -63083,7 +63083,7 @@
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -63108,7 +63108,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr"/>
@@ -63125,7 +63125,7 @@
       </c>
       <c r="AH229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI229" t="inlineStr">
@@ -63135,17 +63135,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL229" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
@@ -63155,67 +63155,67 @@
       </c>
       <c r="AN229" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>88.04</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>98.8632</t>
+          <t>97.4526</t>
         </is>
       </c>
       <c r="AR229" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3432</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.1162</t>
         </is>
       </c>
       <c r="AT229" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.2764</t>
         </is>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
@@ -63263,24 +63263,24 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F230" t="inlineStr">
         <is>
           <t>2026-08-23T00:40:00Z</t>
@@ -63298,12 +63298,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -63312,7 +63312,7 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
@@ -63326,14 +63326,14 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P230" t="n">
-        <v>16.3</v>
+        <v>26</v>
       </c>
       <c r="Q230" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R230" t="n">
         <v>22.6</v>
@@ -63342,10 +63342,10 @@
         <v>40.2</v>
       </c>
       <c r="T230" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U230" t="n">
-        <v>46.5</v>
+        <v>36</v>
       </c>
       <c r="V230" t="inlineStr">
         <is>
@@ -63384,7 +63384,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr"/>
@@ -63401,27 +63401,27 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK230" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL230" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM230" t="inlineStr">
@@ -63431,97 +63431,97 @@
       </c>
       <c r="AN230" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>90.6</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>98.8632</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT230" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD230" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE230" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF230" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG230" t="inlineStr"/>
@@ -63539,27 +63539,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63569,17 +63569,17 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -63588,7 +63588,7 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63606,22 +63606,22 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="Q231" t="n">
-        <v>33.7</v>
+        <v>40</v>
       </c>
       <c r="R231" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S231" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T231" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U231" t="n">
-        <v>0</v>
+        <v>46.5</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -63635,7 +63635,7 @@
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -63660,7 +63660,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr"/>
@@ -63677,134 +63677,134 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>97.0729</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>
@@ -63815,27 +63815,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -63850,12 +63850,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -63878,26 +63878,26 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P232" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q232" t="n">
-        <v>39</v>
+        <v>33.7</v>
       </c>
       <c r="R232" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S232" t="n">
         <v>59.8</v>
       </c>
       <c r="T232" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U232" t="n">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr"/>
@@ -63953,134 +63953,134 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>85.36</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>96.7655</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>0.1111</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>89.16</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE232" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
       <c r="BI232" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ232" t="inlineStr"/>
@@ -64091,27 +64091,27 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -64126,12 +64126,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -64154,26 +64154,26 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>24</v>
+        <v>11.6</v>
       </c>
       <c r="Q233" t="n">
-        <v>21.5</v>
+        <v>39</v>
       </c>
       <c r="R233" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S233" t="n">
         <v>59.8</v>
       </c>
       <c r="T233" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U233" t="n">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -64229,134 +64229,134 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ233" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ233" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.36</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>97.8947</t>
+          <t>96.7655</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>0.3684</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>0.1403</t>
+          <t>0.1111</t>
         </is>
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.3149</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>68.64</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>89.16</t>
         </is>
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="BE233" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>30.46</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
       <c r="BH233" t="inlineStr"/>
       <c r="BI233" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ233" t="inlineStr"/>
@@ -64367,27 +64367,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -64397,17 +64397,17 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -64416,7 +64416,7 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
@@ -64434,22 +64434,22 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Q234" t="n">
-        <v>39.3</v>
+        <v>21.5</v>
       </c>
       <c r="R234" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S234" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T234" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U234" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -64463,7 +64463,7 @@
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -64488,7 +64488,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr"/>
@@ -64505,12 +64505,12 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -64520,12 +64520,12 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
@@ -64535,104 +64535,104 @@
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>97.4351</t>
+          <t>97.8947</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3684</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1403</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.2914</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD234" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE234" t="inlineStr">
         <is>
-          <t>0.1661</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF234" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG234" t="inlineStr"/>
       <c r="BH234" t="inlineStr"/>
       <c r="BI234" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ234" t="inlineStr"/>
@@ -64643,27 +64643,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-22T18:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -64673,17 +64673,17 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -64692,7 +64692,7 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
@@ -64706,26 +64706,26 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P235" t="n">
-        <v>11.1</v>
+        <v>13.5</v>
       </c>
       <c r="Q235" t="n">
-        <v>35</v>
+        <v>39.3</v>
       </c>
       <c r="R235" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S235" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T235" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U235" t="n">
-        <v>27.7</v>
+        <v>19.5</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -64764,7 +64764,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr"/>
@@ -64781,12 +64781,12 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -64796,12 +64796,12 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/23, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 19.2 HR allowed</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
@@ -64811,104 +64811,104 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>86.18</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>96.3935</t>
+          <t>97.4351</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>0.3667</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>0.1036</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>68.73</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>25.09</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>0.1217</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>36.09</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="BD235" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="BE235" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1661</t>
         </is>
       </c>
       <c r="BF235" t="inlineStr">
         <is>
-          <t>29.67</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="BG235" t="inlineStr"/>
       <c r="BH235" t="inlineStr"/>
       <c r="BI235" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ235" t="inlineStr"/>
@@ -64919,27 +64919,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T18:10:00Z</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -64949,22 +64949,22 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L236" t="n">
@@ -64982,26 +64982,26 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P236" t="n">
-        <v>27.9</v>
+        <v>11.1</v>
       </c>
       <c r="Q236" t="n">
-        <v>21.9</v>
+        <v>35</v>
       </c>
       <c r="R236" t="n">
         <v>27.6</v>
       </c>
       <c r="S236" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T236" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U236" t="n">
-        <v>17.3</v>
+        <v>27.7</v>
       </c>
       <c r="V236" t="inlineStr">
         <is>
@@ -65015,7 +65015,7 @@
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -65057,12 +65057,12 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
@@ -65072,119 +65072,119 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 7/23, 0 HR</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.18</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>99.4468</t>
+          <t>96.3935</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>0.4195</t>
+          <t>0.3667</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>0.1501</t>
+          <t>0.1036</t>
         </is>
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>0.3113</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>68.73</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>25.09</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>0.1449</t>
+          <t>0.1217</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>36.09</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE236" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>29.67</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ236" t="inlineStr"/>
@@ -65195,27 +65195,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>500743</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Miguel Rojas</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -65225,26 +65225,26 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L237" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -65258,26 +65258,26 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>18.8</v>
+        <v>27.9</v>
       </c>
       <c r="Q237" t="n">
-        <v>42.6</v>
+        <v>21.9</v>
       </c>
       <c r="R237" t="n">
         <v>27.6</v>
       </c>
       <c r="S237" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T237" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U237" t="n">
-        <v>5.1</v>
+        <v>17.3</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
@@ -65291,7 +65291,7 @@
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y237" t="inlineStr">
@@ -65316,7 +65316,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr"/>
@@ -65333,12 +65333,12 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
@@ -65348,119 +65348,119 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.7% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>98.1355</t>
+          <t>99.4468</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3881</t>
+          <t>0.4195</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1118</t>
+          <t>0.1501</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.3113</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1252</t>
+          <t>0.1449</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -65471,22 +65471,22 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -65501,17 +65501,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -65520,7 +65520,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -65534,26 +65534,26 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>13.1</v>
+        <v>18.8</v>
       </c>
       <c r="Q238" t="n">
-        <v>36.8</v>
+        <v>42.6</v>
       </c>
       <c r="R238" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S238" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T238" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U238" t="n">
-        <v>43.2</v>
+        <v>5.1</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -65609,27 +65609,27 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 2/13, 0 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -65639,104 +65639,104 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>35.47</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>99.1019</t>
+          <t>98.1355</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3089</t>
+          <t>0.3881</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.0798</t>
+          <t>0.1118</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2629</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>68.94</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.1134</t>
+          <t>0.1252</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -65747,22 +65747,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>678011</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Anthony Seigler</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -65782,12 +65782,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -65814,22 +65814,22 @@
         </is>
       </c>
       <c r="P239" t="n">
-        <v>20.2</v>
+        <v>13.1</v>
       </c>
       <c r="Q239" t="n">
-        <v>25.9</v>
+        <v>36.8</v>
       </c>
       <c r="R239" t="n">
-        <v>28.7</v>
+        <v>23.2</v>
       </c>
       <c r="S239" t="n">
         <v>40.2</v>
       </c>
       <c r="T239" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U239" t="n">
-        <v>40.3</v>
+        <v>43.2</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -65868,7 +65868,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr"/>
@@ -65885,27 +65885,27 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
@@ -65915,104 +65915,104 @@
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>97.283</t>
+          <t>99.1019</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3089</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.0798</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>0.3079</t>
+          <t>0.2629</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1134</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE239" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
       <c r="BH239" t="inlineStr"/>
       <c r="BI239" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ239" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -8894,7 +8894,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -14502,34 +14502,30 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17006,7 +17002,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
@@ -18130,7 +18126,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -19230,34 +19226,30 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22030,7 +22022,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -23714,34 +23706,30 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27894,34 +27882,30 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -31818,34 +31802,30 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32666,7 +32646,7 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
@@ -34350,7 +34330,7 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
@@ -41862,34 +41842,30 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42871,27 +42847,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>545121</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Ildemaro Vargas</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -42901,17 +42877,17 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -42920,7 +42896,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="M153" t="inlineStr">
         <is>
@@ -42934,47 +42910,39 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P153" t="n">
-        <v>24.8</v>
+        <v>17.8</v>
       </c>
       <c r="Q153" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="R153" t="n">
         <v>41.7</v>
       </c>
-      <c r="R153" t="n">
-        <v>48.1</v>
-      </c>
       <c r="S153" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T153" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U153" t="n">
-        <v>41.2</v>
+        <v>45.5</v>
       </c>
       <c r="V153" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr"/>
+      <c r="X153" t="inlineStr"/>
+      <c r="Y153" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="Z153" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -42982,17 +42950,17 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr"/>
@@ -43009,142 +42977,142 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>88.36</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>99.034</t>
+          <t>98.628</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>0.3179</t>
+          <t>0.3788</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>0.1162</t>
+          <t>0.1056</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3017</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>14.33</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>0.1365</t>
+          <t>0.1326</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.454</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.189</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH153" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr"/>
@@ -43155,22 +43123,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>545121</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ildemaro Vargas</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -43185,17 +43153,17 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -43204,7 +43172,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -43218,54 +43186,58 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>17.8</v>
+        <v>31.3</v>
       </c>
       <c r="Q154" t="n">
-        <v>49.2</v>
+        <v>14</v>
       </c>
       <c r="R154" t="n">
-        <v>41.7</v>
+        <v>80.2</v>
       </c>
       <c r="S154" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T154" t="n">
         <v>75</v>
       </c>
       <c r="U154" t="n">
-        <v>45.5</v>
+        <v>36</v>
       </c>
       <c r="V154" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr"/>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y154" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -43290,22 +43262,22 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
@@ -43315,112 +43287,112 @@
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>40.04</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>98.628</t>
+          <t>99.6133</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>0.3788</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>0.1056</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.3017</t>
+          <t>0.2857</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>14.33</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>34.18</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>27.04</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>0.1326</t>
+          <t>0.1149</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="BE154" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH154" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI154" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ154" t="inlineStr"/>
@@ -43431,27 +43403,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>650859</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Luis Rengifo</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -43461,17 +43433,17 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -43480,7 +43452,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>41.6</v>
+        <v>41.3</v>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -43494,30 +43466,30 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>31.3</v>
+        <v>16.3</v>
       </c>
       <c r="Q155" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="R155" t="n">
-        <v>80.2</v>
+        <v>48.1</v>
       </c>
       <c r="S155" t="n">
-        <v>52.4</v>
+        <v>71.7</v>
       </c>
       <c r="T155" t="n">
         <v>75</v>
       </c>
       <c r="U155" t="n">
-        <v>36</v>
+        <v>46.5</v>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
@@ -43527,7 +43499,7 @@
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -43537,18 +43509,22 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr"/>
@@ -43565,12 +43541,12 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -43580,127 +43556,127 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Last 7 games: 8/26, 1 HR</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>40.04</t>
+          <t>33.61</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>99.6133</t>
+          <t>97.8176</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.3568</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.2857</t>
+          <t>0.3062</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>70.76</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>14.23</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>27.04</t>
+          <t>18.01</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>0.1149</t>
+          <t>0.0837</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr"/>
@@ -46302,34 +46278,30 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB165" t="inlineStr"/>
       <c r="AC165" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47986,7 +47958,7 @@
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X171" t="inlineStr">
@@ -52939,27 +52911,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>650859</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Luis Rengifo</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-08-23T00:40:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -52969,17 +52941,17 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -52988,7 +52960,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -53002,65 +52974,61 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P189" t="n">
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="Q189" t="n">
-        <v>40</v>
+        <v>36.8</v>
       </c>
       <c r="R189" t="n">
-        <v>48.1</v>
+        <v>50.2</v>
       </c>
       <c r="S189" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T189" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U189" t="n">
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="V189" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr"/>
@@ -53077,127 +53045,127 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 1 HR</t>
+          <t>Last 7 games: 2/22, 0 HR</t>
         </is>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>33.61</t>
+          <t>29.73</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
         <is>
-          <t>97.8176</t>
+          <t>96.8205</t>
         </is>
       </c>
       <c r="AR189" t="inlineStr">
         <is>
-          <t>0.3568</t>
+          <t>0.3457</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1137</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>0.3062</t>
+          <t>0.2989</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>70.76</t>
+          <t>69.12</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>14.23</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>27.52</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>0.0837</t>
+          <t>0.1441</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>87.33</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD189" t="inlineStr">
         <is>
-          <t>0.4319</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE189" t="inlineStr">
         <is>
-          <t>0.1953</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF189" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG189" t="inlineStr">
@@ -53207,12 +53175,12 @@
       </c>
       <c r="BH189" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI189" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ189" t="inlineStr"/>
@@ -53223,56 +53191,56 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>592663</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>J.T. Realmuto</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>36.8</v>
+        <v>36.4</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -53286,26 +53254,26 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>15.9</v>
+        <v>30.5</v>
       </c>
       <c r="Q190" t="n">
-        <v>36.8</v>
+        <v>4.9</v>
       </c>
       <c r="R190" t="n">
-        <v>50.2</v>
+        <v>68.8</v>
       </c>
       <c r="S190" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T190" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U190" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -53319,7 +53287,7 @@
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
@@ -53357,7 +53325,7 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
@@ -53372,12 +53340,12 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM190" t="inlineStr">
@@ -53387,112 +53355,112 @@
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>41.86</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>89.79</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>96.8205</t>
+          <t>100.1831</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>0.3457</t>
+          <t>0.3935</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>0.1137</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>0.2989</t>
+          <t>0.3202</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>41.25</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>25.45</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>0.1441</t>
+          <t>0.1263</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="BD190" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="BE190" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="BF190" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG190" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH190" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI190" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ190" t="inlineStr"/>
@@ -53503,52 +53471,52 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>592663</t>
+          <t>663647</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>J.T. Realmuto</t>
+          <t>Ke'Bryan Hayes</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L191" t="n">
@@ -53566,26 +53534,26 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>30.5</v>
+        <v>31.4</v>
       </c>
       <c r="Q191" t="n">
-        <v>4.9</v>
+        <v>33.7</v>
       </c>
       <c r="R191" t="n">
-        <v>68.8</v>
+        <v>41.7</v>
       </c>
       <c r="S191" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T191" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U191" t="n">
-        <v>9.300000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="V191" t="inlineStr">
         <is>
@@ -53599,7 +53567,7 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -53620,7 +53588,7 @@
       <c r="AB191" t="inlineStr"/>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr"/>
@@ -53637,12 +53605,12 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
@@ -53652,12 +53620,12 @@
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Last 7 games: 3/12, 0 HR</t>
         </is>
       </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.0% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -53667,112 +53635,112 @@
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>7.19</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>41.86</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>89.79</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>100.1831</t>
+          <t>99.7927</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>0.3935</t>
+          <t>0.3847</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>0.3202</t>
+          <t>0.2974</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>41.25</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>0.1263</t>
+          <t>0.0927</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD191" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE191" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH191" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI191" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ191" t="inlineStr"/>
@@ -53783,27 +53751,27 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>663647</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Ke'Bryan Hayes</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -53813,17 +53781,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Christian Scott</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>681035</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -53832,7 +53800,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -53846,26 +53814,26 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>31.4</v>
+        <v>12.1</v>
       </c>
       <c r="Q192" t="n">
-        <v>33.7</v>
+        <v>26.5</v>
       </c>
       <c r="R192" t="n">
-        <v>41.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="S192" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T192" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U192" t="n">
-        <v>19.5</v>
+        <v>21.5</v>
       </c>
       <c r="V192" t="inlineStr">
         <is>
@@ -53874,37 +53842,33 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB192" t="inlineStr"/>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr"/>
@@ -53921,12 +53885,12 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -53936,12 +53900,12 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/12, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -53951,112 +53915,112 @@
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>87.08</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>99.7927</t>
+          <t>97.82</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
         <is>
-          <t>0.3847</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>0.1383</t>
+          <t>0.0973</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>0.2974</t>
+          <t>0.2593</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>70.96</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.43</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>0.0927</t>
+          <t>0.1071</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="BD192" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="BE192" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BG192" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH192" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI192" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ192" t="inlineStr"/>
@@ -54067,27 +54031,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -54097,17 +54061,17 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Christian Scott</t>
+          <t>Drew Anderson</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>681035</t>
+          <t>623454</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -54134,22 +54098,22 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>12.1</v>
+        <v>13.1</v>
       </c>
       <c r="Q193" t="n">
-        <v>26.5</v>
+        <v>36.8</v>
       </c>
       <c r="R193" t="n">
-        <v>68.59999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="S193" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T193" t="n">
         <v>80</v>
       </c>
       <c r="U193" t="n">
-        <v>21.5</v>
+        <v>43.2</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
@@ -54163,7 +54127,7 @@
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
@@ -54201,27 +54165,27 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 6/21, 1 HR</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
@@ -54231,112 +54195,112 @@
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
         <is>
-          <t>97.82</t>
+          <t>99.1019</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.3089</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>0.0973</t>
+          <t>0.0798</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>0.2593</t>
+          <t>0.2629</t>
         </is>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>32.74</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>0.1071</t>
+          <t>0.1134</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD193" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="BE193" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="BG193" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH193" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI193" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ193" t="inlineStr"/>
@@ -54347,27 +54311,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -54382,12 +54346,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Drew Anderson</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>623454</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -54396,7 +54360,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -54410,26 +54374,26 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P194" t="n">
-        <v>13.1</v>
+        <v>36.8</v>
       </c>
       <c r="Q194" t="n">
-        <v>36.8</v>
+        <v>22.7</v>
       </c>
       <c r="R194" t="n">
-        <v>50.2</v>
+        <v>41.1</v>
       </c>
       <c r="S194" t="n">
         <v>44.8</v>
       </c>
       <c r="T194" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U194" t="n">
-        <v>43.2</v>
+        <v>31.9</v>
       </c>
       <c r="V194" t="inlineStr">
         <is>
@@ -54464,7 +54428,7 @@
       <c r="AB194" t="inlineStr"/>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr"/>
@@ -54481,12 +54445,12 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -54496,12 +54460,12 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 4/19, 1 HR</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 11.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM194" t="inlineStr">
@@ -54511,112 +54475,112 @@
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>99.1019</t>
+          <t>100.9026</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
-          <t>0.3089</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>0.0798</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>0.2629</t>
+          <t>0.2796</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>0.1134</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD194" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE194" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF194" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG194" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH194" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI194" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ194" t="inlineStr"/>
@@ -54627,27 +54591,27 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>643376</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -54662,12 +54626,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -54676,7 +54640,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>36.1</v>
+        <v>35.6</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -54690,14 +54654,14 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P195" t="n">
-        <v>36.8</v>
+        <v>20.1</v>
       </c>
       <c r="Q195" t="n">
-        <v>22.7</v>
+        <v>50.2</v>
       </c>
       <c r="R195" t="n">
         <v>41.1</v>
@@ -54709,7 +54673,7 @@
         <v>50</v>
       </c>
       <c r="U195" t="n">
-        <v>31.9</v>
+        <v>0</v>
       </c>
       <c r="V195" t="inlineStr">
         <is>
@@ -54761,127 +54725,127 @@
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 1 HR</t>
+          <t>Last 7 games: 1/16, 0 HR</t>
         </is>
       </c>
       <c r="AL195" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>33.96</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>87.25</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>100.9026</t>
+          <t>97.5999</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.1171</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr">
         <is>
-          <t>0.2796</t>
+          <t>0.2612</t>
         </is>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>70.06</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.1462</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>10.39</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="BD195" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4535</t>
         </is>
       </c>
       <c r="BE195" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1945</t>
         </is>
       </c>
       <c r="BF195" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="BG195" t="inlineStr">
@@ -54896,7 +54860,7 @@
       </c>
       <c r="BI195" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ195" t="inlineStr"/>
@@ -54907,27 +54871,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>666163</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Ben Rortvedt</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -54942,12 +54906,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -54970,26 +54934,26 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P196" t="n">
-        <v>20.1</v>
+        <v>1</v>
       </c>
       <c r="Q196" t="n">
-        <v>50.2</v>
+        <v>42.6</v>
       </c>
       <c r="R196" t="n">
-        <v>41.1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S196" t="n">
         <v>44.8</v>
       </c>
       <c r="T196" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U196" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="V196" t="inlineStr">
         <is>
@@ -55024,7 +54988,7 @@
       <c r="AB196" t="inlineStr"/>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr"/>
@@ -55041,12 +55005,12 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ196" t="inlineStr">
@@ -55056,127 +55020,127 @@
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/16, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL196" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>12.25</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>87.25</t>
+          <t>82.81</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
         <is>
-          <t>97.5999</t>
+          <t>92.3067</t>
         </is>
       </c>
       <c r="AR196" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>0.1171</t>
+          <t>0.0438</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr">
         <is>
-          <t>0.2612</t>
+          <t>0.2218</t>
         </is>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>70.06</t>
+          <t>67.72</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>0.1462</t>
+          <t>0.0159</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="BD196" t="inlineStr">
         <is>
-          <t>0.4535</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="BE196" t="inlineStr">
         <is>
-          <t>0.1945</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF196" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="BG196" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH196" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI196" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ196" t="inlineStr"/>
@@ -55187,22 +55151,22 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>666163</t>
+          <t>681508</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ben Rortvedt</t>
+          <t>Mickey Gasper</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -55222,12 +55186,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Blade Tidwell</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>694918</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -55236,7 +55200,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -55250,26 +55214,26 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1</v>
+        <v>22.4</v>
       </c>
       <c r="Q197" t="n">
-        <v>42.6</v>
+        <v>25.9</v>
       </c>
       <c r="R197" t="n">
-        <v>72.59999999999999</v>
+        <v>36.7</v>
       </c>
       <c r="S197" t="n">
         <v>44.8</v>
       </c>
       <c r="T197" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U197" t="n">
-        <v>14.1</v>
+        <v>67</v>
       </c>
       <c r="V197" t="inlineStr">
         <is>
@@ -55304,7 +55268,7 @@
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr"/>
@@ -55321,27 +55285,27 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 11.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
@@ -55351,112 +55315,112 @@
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>82.81</t>
+          <t>88.15</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>92.3067</t>
+          <t>98.2082</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.3446</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>0.0438</t>
+          <t>0.1251</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>0.2218</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>67.72</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>0.0159</t>
+          <t>0.1153</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="BD197" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3849</t>
         </is>
       </c>
       <c r="BE197" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>21.73</t>
         </is>
       </c>
       <c r="BG197" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH197" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BI197" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ197" t="inlineStr"/>
@@ -55467,27 +55431,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>681508</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Mickey Gasper</t>
+          <t>Drew Romo</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -55502,12 +55466,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Blade Tidwell</t>
+          <t>Christian Scott</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>681035</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -55516,7 +55480,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>35.5</v>
+        <v>35.3</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -55534,13 +55498,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>22.4</v>
+        <v>10.2</v>
       </c>
       <c r="Q198" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="R198" t="n">
-        <v>36.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="S198" t="n">
         <v>44.8</v>
@@ -55549,7 +55513,7 @@
         <v>75</v>
       </c>
       <c r="U198" t="n">
-        <v>67</v>
+        <v>48.7</v>
       </c>
       <c r="V198" t="inlineStr">
         <is>
@@ -55584,7 +55548,7 @@
       <c r="AB198" t="inlineStr"/>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr"/>
@@ -55611,17 +55575,17 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL198" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 2.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.8% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM198" t="inlineStr">
@@ -55631,112 +55595,112 @@
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>33.86</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>88.15</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>98.2082</t>
+          <t>95.1095</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>0.3446</t>
+          <t>0.2051</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>0.1251</t>
+          <t>0.0784</t>
         </is>
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>0.2899</t>
+          <t>0.1743</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>0.1153</t>
+          <t>0.1148</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="BD198" t="inlineStr">
         <is>
-          <t>0.3849</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="BE198" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>21.73</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BG198" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH198" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI198" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ198" t="inlineStr"/>
@@ -55747,56 +55711,56 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T22:05:00Z</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Christian Scott</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>681035</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>35.3</v>
+        <v>35</v>
       </c>
       <c r="M199" t="inlineStr">
         <is>
@@ -55810,26 +55774,26 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P199" t="n">
-        <v>10.2</v>
+        <v>7.7</v>
       </c>
       <c r="Q199" t="n">
-        <v>25.7</v>
+        <v>4.9</v>
       </c>
       <c r="R199" t="n">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="S199" t="n">
-        <v>44.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T199" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U199" t="n">
-        <v>48.7</v>
+        <v>63.3</v>
       </c>
       <c r="V199" t="inlineStr">
         <is>
@@ -55843,7 +55807,7 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -55881,27 +55845,27 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 14/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.8% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.0% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
@@ -55911,97 +55875,97 @@
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>86.59</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>95.1095</t>
+          <t>94.0058</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>0.2051</t>
+          <t>0.3777</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>0.0784</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>0.1743</t>
+          <t>0.3072</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>62.99</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>0.1148</t>
+          <t>0.1154</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="BE199" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr">
@@ -56011,12 +55975,12 @@
       </c>
       <c r="BH199" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI199" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ199" t="inlineStr"/>
@@ -56027,52 +55991,52 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-08-22T22:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L200" t="n">
@@ -56090,26 +56054,26 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P200" t="n">
-        <v>7.7</v>
+        <v>24</v>
       </c>
       <c r="Q200" t="n">
-        <v>4.9</v>
+        <v>21.5</v>
       </c>
       <c r="R200" t="n">
-        <v>68.8</v>
+        <v>41.1</v>
       </c>
       <c r="S200" t="n">
-        <v>94.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T200" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U200" t="n">
-        <v>63.3</v>
+        <v>0</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
@@ -56123,7 +56087,7 @@
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y200" t="inlineStr">
@@ -56144,7 +56108,7 @@
       <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr"/>
@@ -56161,27 +56125,27 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Contact streak: 14/31 over last 7 games</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.0% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
@@ -56191,112 +56155,112 @@
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>94.0058</t>
+          <t>97.8947</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3777</t>
+          <t>0.3684</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1403</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.3072</t>
+          <t>0.2914</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>62.99</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.1154</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG200" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH200" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -56307,12 +56271,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>695720</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Tommy White</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -56337,7 +56301,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -56356,7 +56320,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -56370,26 +56334,26 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P201" t="n">
-        <v>24</v>
+        <v>15.3</v>
       </c>
       <c r="Q201" t="n">
-        <v>21.5</v>
+        <v>22.7</v>
       </c>
       <c r="R201" t="n">
         <v>41.1</v>
       </c>
       <c r="S201" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T201" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U201" t="n">
-        <v>0</v>
+        <v>57.8</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
@@ -56403,7 +56367,7 @@
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y201" t="inlineStr">
@@ -56424,7 +56388,7 @@
       <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr"/>
@@ -56441,27 +56405,27 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
@@ -56471,67 +56435,67 @@
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>97.8947</t>
+          <t>96.7187</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>0.3684</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>0.1403</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>0.2914</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
@@ -56587,27 +56551,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>695720</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tommy White</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-22T23:05:00Z</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -56617,17 +56581,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -56636,7 +56600,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -56650,26 +56614,26 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P202" t="n">
-        <v>15.3</v>
+        <v>5.6</v>
       </c>
       <c r="Q202" t="n">
-        <v>22.7</v>
+        <v>42.1</v>
       </c>
       <c r="R202" t="n">
-        <v>41.1</v>
+        <v>55.6</v>
       </c>
       <c r="S202" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T202" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U202" t="n">
-        <v>57.8</v>
+        <v>24.9</v>
       </c>
       <c r="V202" t="inlineStr">
         <is>
@@ -56683,7 +56647,7 @@
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr">
@@ -56704,7 +56668,7 @@
       <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr"/>
@@ -56726,22 +56690,22 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM202" t="inlineStr">
@@ -56751,112 +56715,112 @@
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>23.18</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>96.7187</t>
+          <t>95.4095</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.0759</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.2512</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.35</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.0836</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="BD202" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4201</t>
         </is>
       </c>
       <c r="BE202" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1672</t>
         </is>
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>27.43</t>
         </is>
       </c>
       <c r="BG202" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH202" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI202" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ202" t="inlineStr"/>
@@ -56867,27 +56831,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-22T23:05:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -56897,17 +56861,17 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Christian Scott</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>681035</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -56930,26 +56894,26 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P203" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="Q203" t="n">
-        <v>42.1</v>
+        <v>26.5</v>
       </c>
       <c r="R203" t="n">
-        <v>55.6</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="S203" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T203" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U203" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="V203" t="inlineStr">
         <is>
@@ -56963,7 +56927,7 @@
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y203" t="inlineStr">
@@ -56984,7 +56948,7 @@
       <c r="AB203" t="inlineStr"/>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr"/>
@@ -57001,12 +56965,12 @@
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ203" t="inlineStr">
@@ -57016,12 +56980,12 @@
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL203" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.9% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM203" t="inlineStr">
@@ -57031,112 +56995,112 @@
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>23.18</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.85</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
         <is>
-          <t>95.4095</t>
+          <t>97.4105</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.3337</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>0.0759</t>
+          <t>0.0947</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr">
         <is>
-          <t>0.2512</t>
+          <t>0.2944</t>
         </is>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>68.35</t>
+          <t>67.12</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>0.0836</t>
+          <t>0.1125</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="BD203" t="inlineStr">
         <is>
-          <t>0.4201</t>
+          <t>0.356</t>
         </is>
       </c>
       <c r="BE203" t="inlineStr">
         <is>
-          <t>0.1672</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>27.43</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="BG203" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH203" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI203" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ203" t="inlineStr"/>
@@ -57147,27 +57111,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Héctor Rodríguez</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-23T00:10:00Z</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -57177,17 +57141,17 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Christian Scott</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>681035</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -57196,7 +57160,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>34.5</v>
+        <v>33.4</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -57210,23 +57174,23 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P204" t="n">
-        <v>13</v>
+        <v>13.7</v>
       </c>
       <c r="Q204" t="n">
-        <v>26.5</v>
+        <v>33.7</v>
       </c>
       <c r="R204" t="n">
-        <v>68.59999999999999</v>
+        <v>41.7</v>
       </c>
       <c r="S204" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T204" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U204" t="n">
         <v>0</v>
@@ -57243,7 +57207,7 @@
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y204" t="inlineStr">
@@ -57264,7 +57228,7 @@
       <c r="AB204" t="inlineStr"/>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr"/>
@@ -57281,12 +57245,12 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ204" t="inlineStr">
@@ -57296,12 +57260,12 @@
       </c>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL204" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM204" t="inlineStr">
@@ -57311,112 +57275,112 @@
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>87.85</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
         <is>
-          <t>97.4105</t>
+          <t>97.0729</t>
         </is>
       </c>
       <c r="AR204" t="inlineStr">
         <is>
-          <t>0.3337</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>0.0947</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="AT204" t="inlineStr">
         <is>
-          <t>0.2944</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>67.12</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>0.1125</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD204" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.3902</t>
         </is>
       </c>
       <c r="BE204" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="BG204" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH204" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI204" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ204" t="inlineStr"/>
@@ -57427,22 +57391,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Héctor Rodríguez</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -57457,17 +57421,17 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -57490,26 +57454,26 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P205" t="n">
-        <v>13.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q205" t="n">
-        <v>33.7</v>
+        <v>14.3</v>
       </c>
       <c r="R205" t="n">
-        <v>41.7</v>
+        <v>80.2</v>
       </c>
       <c r="S205" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T205" t="n">
         <v>80</v>
       </c>
       <c r="U205" t="n">
-        <v>0</v>
+        <v>30.3</v>
       </c>
       <c r="V205" t="inlineStr">
         <is>
@@ -57518,37 +57482,33 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB205" t="inlineStr"/>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr"/>
@@ -57565,27 +57525,27 @@
       </c>
       <c r="AH205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 4/20, 1 HR</t>
         </is>
       </c>
       <c r="AL205" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 7.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM205" t="inlineStr">
@@ -57595,112 +57555,112 @@
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
+          <t>81.87</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>93.6761</t>
+        </is>
+      </c>
+      <c r="AR205" t="inlineStr">
+        <is>
+          <t>0.3122</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>0.0959</t>
+        </is>
+      </c>
+      <c r="AT205" t="inlineStr">
+        <is>
+          <t>0.2818</t>
+        </is>
+      </c>
+      <c r="AU205" t="inlineStr">
+        <is>
+          <t>70.36</t>
+        </is>
+      </c>
+      <c r="AV205" t="inlineStr">
+        <is>
+          <t>5.74</t>
+        </is>
+      </c>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>33.19</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>0.0784</t>
+        </is>
+      </c>
+      <c r="BA205" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="BB205" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="BC205" t="inlineStr">
+        <is>
           <t>88.0</t>
         </is>
       </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>97.0729</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>0.194</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr">
-        <is>
-          <t>0.037</t>
-        </is>
-      </c>
-      <c r="AT205" t="inlineStr">
-        <is>
-          <t>0.198</t>
-        </is>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AV205" t="inlineStr">
-        <is>
-          <t>51.6</t>
-        </is>
-      </c>
-      <c r="AW205" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="AX205" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="AY205" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AZ205" t="inlineStr">
-        <is>
-          <t>0.029</t>
-        </is>
-      </c>
-      <c r="BA205" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BB205" t="inlineStr">
-        <is>
-          <t>34.94</t>
-        </is>
-      </c>
-      <c r="BC205" t="inlineStr">
-        <is>
-          <t>88.08</t>
-        </is>
-      </c>
       <c r="BD205" t="inlineStr">
         <is>
-          <t>0.3902</t>
+          <t>0.338</t>
         </is>
       </c>
       <c r="BE205" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.106</t>
         </is>
       </c>
       <c r="BF205" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="BG205" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH205" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI205" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ205" t="inlineStr"/>
@@ -57711,27 +57671,27 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>683766</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-08-23T00:10:00Z</t>
+          <t>2026-08-22T23:15:00Z</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -57741,26 +57701,26 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L206" t="n">
-        <v>33.4</v>
+        <v>33.1</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -57774,26 +57734,26 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P206" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="Q206" t="n">
-        <v>14.3</v>
+        <v>23.7</v>
       </c>
       <c r="R206" t="n">
-        <v>80.2</v>
+        <v>36.7</v>
       </c>
       <c r="S206" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T206" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U206" t="n">
-        <v>30.3</v>
+        <v>21.1</v>
       </c>
       <c r="V206" t="inlineStr">
         <is>
@@ -57807,7 +57767,7 @@
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y206" t="inlineStr">
@@ -57845,27 +57805,27 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 1 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL206" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.3% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM206" t="inlineStr">
@@ -57875,92 +57835,92 @@
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AQ206" t="inlineStr">
         <is>
-          <t>93.6761</t>
+          <t>97.9198</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
         <is>
-          <t>0.3122</t>
+          <t>0.3236</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
         <is>
-          <t>0.0959</t>
+          <t>0.0963</t>
         </is>
       </c>
       <c r="AT206" t="inlineStr">
         <is>
-          <t>0.2818</t>
+          <t>0.2634</t>
         </is>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>40.05</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>33.19</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>0.0784</t>
+          <t>0.069</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="BD206" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>0.412</t>
         </is>
       </c>
       <c r="BE206" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF206" t="inlineStr">
@@ -57970,17 +57930,17 @@
       </c>
       <c r="BG206" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH206" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BI206" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ206" t="inlineStr"/>
@@ -57991,22 +57951,22 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>683766</t>
+          <t>660844</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Leo Rivas</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -58021,17 +57981,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Patrick Sandoval</t>
+          <t>David Peterson</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>663776</t>
+          <t>656849</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -58040,7 +58000,7 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="M207" t="inlineStr">
         <is>
@@ -58058,22 +58018,22 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="Q207" t="n">
-        <v>23.7</v>
+        <v>34.8</v>
       </c>
       <c r="R207" t="n">
-        <v>36.7</v>
+        <v>62.4</v>
       </c>
       <c r="S207" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T207" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U207" t="n">
-        <v>21.1</v>
+        <v>12</v>
       </c>
       <c r="V207" t="inlineStr">
         <is>
@@ -58087,7 +58047,7 @@
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
@@ -58108,7 +58068,7 @@
       <c r="AB207" t="inlineStr"/>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr"/>
@@ -58125,12 +58085,12 @@
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -58140,12 +58100,12 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 2/10, 0 HR</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 3.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
@@ -58155,112 +58115,112 @@
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.37</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>97.9198</t>
+          <t>93.7275</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
         <is>
-          <t>0.3236</t>
+          <t>0.2359</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>0.0963</t>
+          <t>0.0693</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>0.2634</t>
+          <t>0.2558</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>40.05</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>29.88</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.0519</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>42.64</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="BD207" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>0.414</t>
         </is>
       </c>
       <c r="BE207" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1405</t>
         </is>
       </c>
       <c r="BF207" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="BG207" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH207" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI207" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ207" t="inlineStr"/>
@@ -58271,27 +58231,27 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>660844</t>
+          <t>622268</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Leo Rivas</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-08-22T23:15:00Z</t>
+          <t>2026-08-22T23:10:00Z</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -58301,26 +58261,26 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>David Peterson</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>656849</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L208" t="n">
-        <v>32.9</v>
+        <v>32.3</v>
       </c>
       <c r="M208" t="inlineStr">
         <is>
@@ -58338,22 +58298,22 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>4.9</v>
+        <v>14.7</v>
       </c>
       <c r="Q208" t="n">
-        <v>34.8</v>
+        <v>22.7</v>
       </c>
       <c r="R208" t="n">
-        <v>62.4</v>
+        <v>41.1</v>
       </c>
       <c r="S208" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T208" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U208" t="n">
-        <v>12</v>
+        <v>26.1</v>
       </c>
       <c r="V208" t="inlineStr">
         <is>
@@ -58367,7 +58327,7 @@
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y208" t="inlineStr">
@@ -58405,12 +58365,12 @@
       </c>
       <c r="AH208" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
@@ -58420,12 +58380,12 @@
       </c>
       <c r="AK208" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/10, 0 HR</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL208" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.4% barrel, 11.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
         </is>
       </c>
       <c r="AM208" t="inlineStr">
@@ -58435,112 +58395,112 @@
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>34.77</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>86.37</t>
+          <t>89.17</t>
         </is>
       </c>
       <c r="AQ208" t="inlineStr">
         <is>
-          <t>93.7275</t>
+          <t>97.7157</t>
         </is>
       </c>
       <c r="AR208" t="inlineStr">
         <is>
-          <t>0.2359</t>
+          <t>0.3562</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr">
         <is>
-          <t>0.0693</t>
+          <t>0.0956</t>
         </is>
       </c>
       <c r="AT208" t="inlineStr">
         <is>
-          <t>0.2558</t>
+          <t>0.3055</t>
         </is>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>21.53</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>0.0519</t>
+          <t>0.1085</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>42.64</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="BD208" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>0.3397</t>
         </is>
       </c>
       <c r="BE208" t="inlineStr">
         <is>
-          <t>0.1405</t>
+          <t>0.1304</t>
         </is>
       </c>
       <c r="BF208" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="BG208" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH208" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI208" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ208" t="inlineStr"/>
@@ -58551,27 +58511,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>666023</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Freddy Fermin</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-08-22T23:10:00Z</t>
+          <t>2026-08-23T00:40:00Z</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -58581,17 +58541,17 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -58600,7 +58560,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -58614,30 +58574,30 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P209" t="n">
-        <v>14.7</v>
+        <v>13.7</v>
       </c>
       <c r="Q209" t="n">
-        <v>22.7</v>
+        <v>41.7</v>
       </c>
       <c r="R209" t="n">
-        <v>41.1</v>
+        <v>48.1</v>
       </c>
       <c r="S209" t="n">
-        <v>52.4</v>
+        <v>40.2</v>
       </c>
       <c r="T209" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U209" t="n">
-        <v>26.1</v>
+        <v>5.7</v>
       </c>
       <c r="V209" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W209" t="inlineStr">
@@ -58647,7 +58607,7 @@
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr">
@@ -58657,15 +58617,19 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC209" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -58685,12 +58649,12 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
@@ -58700,127 +58664,127 @@
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 11.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>89.17</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
         <is>
-          <t>97.7157</t>
+          <t>97.0054</t>
         </is>
       </c>
       <c r="AR209" t="inlineStr">
         <is>
-          <t>0.3562</t>
+          <t>0.3154</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>0.0956</t>
+          <t>0.1016</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>0.3055</t>
+          <t>0.2665</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>69.78</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.48</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>0.1085</t>
+          <t>0.1055</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>87.33</t>
         </is>
       </c>
       <c r="BD209" t="inlineStr">
         <is>
-          <t>0.3397</t>
+          <t>0.4319</t>
         </is>
       </c>
       <c r="BE209" t="inlineStr">
         <is>
-          <t>0.1304</t>
+          <t>0.1953</t>
         </is>
       </c>
       <c r="BF209" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BG209" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH209" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI209" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ209" t="inlineStr"/>

--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -24452,7 +24452,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -31984,7 +31984,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -35848,7 +35848,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36688,7 +36688,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -40300,7 +40300,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -40860,7 +40860,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -41956,7 +41956,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -42236,7 +42236,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -45312,7 +45312,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -51468,7 +51468,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -56554,7 +56554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -60190,7 +60190,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -61030,7 +61030,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8828,7 +8828,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -16920,7 +16920,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17200,7 +17200,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -18576,7 +18576,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -19972,7 +19972,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21092,7 +21092,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -22492,7 +22492,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29464,7 +29464,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -30584,7 +30584,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -31144,7 +31144,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -31424,7 +31424,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -32264,7 +32264,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -32800,7 +32800,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -34448,7 +34448,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -34728,7 +34728,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -35008,7 +35008,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -36128,7 +36128,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -36968,7 +36968,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -40580,7 +40580,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -41676,7 +41676,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -42796,7 +42796,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -43076,7 +43076,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -44196,7 +44196,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -45032,7 +45032,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -45592,7 +45592,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -47268,7 +47268,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -48108,7 +48108,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -48388,7 +48388,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -48948,7 +48948,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -49228,7 +49228,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -49508,7 +49508,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -50068,7 +50068,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -50628,7 +50628,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -50908,7 +50908,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -51188,7 +51188,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -51748,7 +51748,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -53708,7 +53708,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -54268,7 +54268,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -54548,7 +54548,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -55388,7 +55388,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -56834,7 +56834,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -57954,7 +57954,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -58514,7 +58514,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -59074,7 +59074,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -59354,7 +59354,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -59910,7 +59910,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -60470,7 +60470,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -60750,7 +60750,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-22.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-22.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -14984,7 +14984,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -19132,7 +19132,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -27784,7 +27784,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -29184,7 +29184,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -32544,7 +32544,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -33912,7 +33912,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -34192,7 +34192,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -35288,7 +35288,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -35568,7 +35568,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -37248,7 +37248,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -37808,7 +37808,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -38368,7 +38368,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -38648,7 +38648,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -39208,7 +39208,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -41420,7 +41420,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -43916,7 +43916,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -44476,7 +44476,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -45872,7 +45872,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -46152,7 +46152,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -47548,7 +47548,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -49788,7 +49788,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -50348,7 +50348,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -52028,7 +52028,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -52868,7 +52868,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -53428,7 +53428,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -53988,7 +53988,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -54828,7 +54828,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -55108,7 +55108,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -55668,7 +55668,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -56274,7 +56274,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -57114,7 +57114,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -57394,7 +57394,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -57674,7 +57674,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -58234,7 +58234,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -61310,7 +61310,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -61566,7 +61566,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
